--- a/core_lines.xlsx
+++ b/core_lines.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/66232404f46f11b2/Economic Research/Inflation Risk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/66232404f46f11b2/Economic Research/Inflation/Trimmed Mean PCE Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{788677E2-C94D-4AE8-87E8-65299C362742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAA99B59-6DAA-4A58-9747-B14A25F7D4D1}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{788677E2-C94D-4AE8-87E8-65299C362742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19C8F01E-E6DB-4D0B-8902-F50246640377}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{78D331E5-4456-4953-A1CF-A1635BE4E961}"/>
   </bookViews>
@@ -32,14 +32,14 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="237">
   <si>
     <t xml:space="preserve">                                New autos</t>
   </si>
@@ -743,16 +743,13 @@
     <t>DMHSRG</t>
   </si>
   <si>
-    <t>Line</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
     <t>Code</t>
   </si>
   <si>
-    <t>Space Count</t>
+    <t>Line Item</t>
   </si>
 </sst>
 </file>
@@ -831,10 +828,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1164,17 +1157,15 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>237</v>
-      </c>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
@@ -1186,10 +1177,6 @@
       <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D2">
-        <f t="shared" ref="D2:D27" si="0">LEN(B2)-LEN(TRIM(B2))</f>
-        <v>32</v>
-      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
@@ -1201,10 +1188,6 @@
       <c r="C3" t="s">
         <v>3</v>
       </c>
-      <c r="D3">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
@@ -1216,10 +1199,6 @@
       <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
@@ -1231,10 +1210,6 @@
       <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
@@ -1246,10 +1221,6 @@
       <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
@@ -1261,10 +1232,6 @@
       <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
@@ -1276,10 +1243,6 @@
       <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
@@ -1291,10 +1254,6 @@
       <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
@@ -1306,10 +1265,6 @@
       <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
@@ -1321,10 +1276,6 @@
       <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
@@ -1336,10 +1287,6 @@
       <c r="C12" t="s">
         <v>21</v>
       </c>
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
@@ -1351,10 +1298,6 @@
       <c r="C13" t="s">
         <v>23</v>
       </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
@@ -1366,10 +1309,6 @@
       <c r="C14" t="s">
         <v>25</v>
       </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
@@ -1381,10 +1320,6 @@
       <c r="C15" t="s">
         <v>27</v>
       </c>
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
@@ -1396,12 +1331,8 @@
       <c r="C16" t="s">
         <v>29</v>
       </c>
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>37</v>
       </c>
@@ -1411,12 +1342,8 @@
       <c r="C17" t="s">
         <v>31</v>
       </c>
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>40</v>
       </c>
@@ -1426,12 +1353,8 @@
       <c r="C18" t="s">
         <v>33</v>
       </c>
-      <c r="D18">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>47</v>
       </c>
@@ -1441,12 +1364,8 @@
       <c r="C19" t="s">
         <v>35</v>
       </c>
-      <c r="D19">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>48</v>
       </c>
@@ -1456,12 +1375,8 @@
       <c r="C20" t="s">
         <v>37</v>
       </c>
-      <c r="D20">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>54</v>
       </c>
@@ -1471,12 +1386,8 @@
       <c r="C21" t="s">
         <v>39</v>
       </c>
-      <c r="D21">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>55</v>
       </c>
@@ -1486,12 +1397,8 @@
       <c r="C22" t="s">
         <v>41</v>
       </c>
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>56</v>
       </c>
@@ -1501,12 +1408,8 @@
       <c r="C23" t="s">
         <v>43</v>
       </c>
-      <c r="D23">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>60</v>
       </c>
@@ -1516,12 +1419,8 @@
       <c r="C24" t="s">
         <v>45</v>
       </c>
-      <c r="D24">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>61</v>
       </c>
@@ -1531,12 +1430,8 @@
       <c r="C25" t="s">
         <v>47</v>
       </c>
-      <c r="D25">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>64</v>
       </c>
@@ -1546,12 +1441,8 @@
       <c r="C26" t="s">
         <v>49</v>
       </c>
-      <c r="D26">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>65</v>
       </c>
@@ -1561,12 +1452,8 @@
       <c r="C27" t="s">
         <v>51</v>
       </c>
-      <c r="D27">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>67</v>
       </c>
@@ -1576,12 +1463,8 @@
       <c r="C28" t="s">
         <v>53</v>
       </c>
-      <c r="D28">
-        <f t="shared" ref="D28:D43" si="1">LEN(B28)-LEN(TRIM(B28))</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>68</v>
       </c>
@@ -1591,12 +1474,8 @@
       <c r="C29" t="s">
         <v>55</v>
       </c>
-      <c r="D29">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>69</v>
       </c>
@@ -1606,12 +1485,8 @@
       <c r="C30" t="s">
         <v>57</v>
       </c>
-      <c r="D30">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>70</v>
       </c>
@@ -1621,12 +1496,8 @@
       <c r="C31" t="s">
         <v>59</v>
       </c>
-      <c r="D31">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>71</v>
       </c>
@@ -1636,12 +1507,8 @@
       <c r="C32" t="s">
         <v>61</v>
       </c>
-      <c r="D32">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>106</v>
       </c>
@@ -1651,12 +1518,8 @@
       <c r="C33" t="s">
         <v>63</v>
       </c>
-      <c r="D33">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>107</v>
       </c>
@@ -1666,12 +1529,8 @@
       <c r="C34" t="s">
         <v>65</v>
       </c>
-      <c r="D34">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>108</v>
       </c>
@@ -1681,12 +1540,8 @@
       <c r="C35" t="s">
         <v>67</v>
       </c>
-      <c r="D35">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>110</v>
       </c>
@@ -1696,12 +1551,8 @@
       <c r="C36" t="s">
         <v>69</v>
       </c>
-      <c r="D36">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>111</v>
       </c>
@@ -1711,12 +1562,8 @@
       <c r="C37" t="s">
         <v>71</v>
       </c>
-      <c r="D37">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>112</v>
       </c>
@@ -1726,12 +1573,8 @@
       <c r="C38" t="s">
         <v>73</v>
       </c>
-      <c r="D38">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>122</v>
       </c>
@@ -1741,12 +1584,8 @@
       <c r="C39" t="s">
         <v>75</v>
       </c>
-      <c r="D39">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>125</v>
       </c>
@@ -1756,12 +1595,8 @@
       <c r="C40" t="s">
         <v>77</v>
       </c>
-      <c r="D40">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>127</v>
       </c>
@@ -1771,12 +1606,8 @@
       <c r="C41" t="s">
         <v>79</v>
       </c>
-      <c r="D41">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>128</v>
       </c>
@@ -1786,12 +1617,8 @@
       <c r="C42" t="s">
         <v>81</v>
       </c>
-      <c r="D42">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>129</v>
       </c>
@@ -1801,12 +1628,8 @@
       <c r="C43" t="s">
         <v>83</v>
       </c>
-      <c r="D43">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>130</v>
       </c>
@@ -1816,12 +1639,8 @@
       <c r="C44" t="s">
         <v>85</v>
       </c>
-      <c r="D44">
-        <f t="shared" ref="D44:D67" si="2">LEN(B44)-LEN(TRIM(B44))</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>132</v>
       </c>
@@ -1831,12 +1650,8 @@
       <c r="C45" t="s">
         <v>87</v>
       </c>
-      <c r="D45">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>133</v>
       </c>
@@ -1846,12 +1661,8 @@
       <c r="C46" t="s">
         <v>89</v>
       </c>
-      <c r="D46">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>134</v>
       </c>
@@ -1861,12 +1672,8 @@
       <c r="C47" t="s">
         <v>91</v>
       </c>
-      <c r="D47">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>135</v>
       </c>
@@ -1876,12 +1683,8 @@
       <c r="C48" t="s">
         <v>93</v>
       </c>
-      <c r="D48">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>136</v>
       </c>
@@ -1891,12 +1694,8 @@
       <c r="C49" t="s">
         <v>95</v>
       </c>
-      <c r="D49">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>138</v>
       </c>
@@ -1906,12 +1705,8 @@
       <c r="C50" t="s">
         <v>97</v>
       </c>
-      <c r="D50">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>139</v>
       </c>
@@ -1921,12 +1716,8 @@
       <c r="C51" t="s">
         <v>99</v>
       </c>
-      <c r="D51">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>140</v>
       </c>
@@ -1936,12 +1727,8 @@
       <c r="C52" t="s">
         <v>101</v>
       </c>
-      <c r="D52">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>141</v>
       </c>
@@ -1951,12 +1738,8 @@
       <c r="C53" t="s">
         <v>103</v>
       </c>
-      <c r="D53">
-        <f t="shared" si="2"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>143</v>
       </c>
@@ -1966,12 +1749,8 @@
       <c r="C54" t="s">
         <v>105</v>
       </c>
-      <c r="D54">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>144</v>
       </c>
@@ -1981,12 +1760,8 @@
       <c r="C55" t="s">
         <v>107</v>
       </c>
-      <c r="D55">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>154</v>
       </c>
@@ -1996,12 +1771,8 @@
       <c r="C56" t="s">
         <v>109</v>
       </c>
-      <c r="D56">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>160</v>
       </c>
@@ -2011,12 +1782,8 @@
       <c r="C57" t="s">
         <v>111</v>
       </c>
-      <c r="D57">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>163</v>
       </c>
@@ -2026,12 +1793,8 @@
       <c r="C58" t="s">
         <v>113</v>
       </c>
-      <c r="D58">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>164</v>
       </c>
@@ -2041,12 +1804,8 @@
       <c r="C59" t="s">
         <v>115</v>
       </c>
-      <c r="D59">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>166</v>
       </c>
@@ -2056,12 +1815,8 @@
       <c r="C60" t="s">
         <v>117</v>
       </c>
-      <c r="D60">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>174</v>
       </c>
@@ -2071,12 +1826,8 @@
       <c r="C61" t="s">
         <v>119</v>
       </c>
-      <c r="D61">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>175</v>
       </c>
@@ -2086,12 +1837,8 @@
       <c r="C62" t="s">
         <v>121</v>
       </c>
-      <c r="D62">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>176</v>
       </c>
@@ -2101,12 +1848,8 @@
       <c r="C63" t="s">
         <v>123</v>
       </c>
-      <c r="D63">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>183</v>
       </c>
@@ -2116,12 +1859,8 @@
       <c r="C64" t="s">
         <v>125</v>
       </c>
-      <c r="D64">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>187</v>
       </c>
@@ -2131,12 +1870,8 @@
       <c r="C65" t="s">
         <v>127</v>
       </c>
-      <c r="D65">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>192</v>
       </c>
@@ -2146,12 +1881,8 @@
       <c r="C66" t="s">
         <v>129</v>
       </c>
-      <c r="D66">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>193</v>
       </c>
@@ -2161,12 +1892,8 @@
       <c r="C67" t="s">
         <v>131</v>
       </c>
-      <c r="D67">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>200</v>
       </c>
@@ -2176,12 +1903,8 @@
       <c r="C68" t="s">
         <v>133</v>
       </c>
-      <c r="D68">
-        <f t="shared" ref="D68:D90" si="3">LEN(B68)-LEN(TRIM(B68))</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>207</v>
       </c>
@@ -2191,12 +1914,8 @@
       <c r="C69" t="s">
         <v>135</v>
       </c>
-      <c r="D69">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>208</v>
       </c>
@@ -2206,12 +1925,8 @@
       <c r="C70" t="s">
         <v>137</v>
       </c>
-      <c r="D70">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>211</v>
       </c>
@@ -2221,12 +1936,8 @@
       <c r="C71" t="s">
         <v>139</v>
       </c>
-      <c r="D71">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>212</v>
       </c>
@@ -2236,12 +1947,8 @@
       <c r="C72" t="s">
         <v>141</v>
       </c>
-      <c r="D72">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>213</v>
       </c>
@@ -2251,12 +1958,8 @@
       <c r="C73" t="s">
         <v>143</v>
       </c>
-      <c r="D73">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>217</v>
       </c>
@@ -2266,12 +1969,8 @@
       <c r="C74" t="s">
         <v>145</v>
       </c>
-      <c r="D74">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>219</v>
       </c>
@@ -2281,12 +1980,8 @@
       <c r="C75" t="s">
         <v>147</v>
       </c>
-      <c r="D75">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>220</v>
       </c>
@@ -2296,12 +1991,8 @@
       <c r="C76" t="s">
         <v>149</v>
       </c>
-      <c r="D76">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>221</v>
       </c>
@@ -2311,12 +2002,8 @@
       <c r="C77" t="s">
         <v>151</v>
       </c>
-      <c r="D77">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>222</v>
       </c>
@@ -2326,12 +2013,8 @@
       <c r="C78" t="s">
         <v>153</v>
       </c>
-      <c r="D78">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>223</v>
       </c>
@@ -2341,12 +2024,8 @@
       <c r="C79" t="s">
         <v>155</v>
       </c>
-      <c r="D79">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>227</v>
       </c>
@@ -2356,12 +2035,8 @@
       <c r="C80" t="s">
         <v>157</v>
       </c>
-      <c r="D80">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>228</v>
       </c>
@@ -2371,12 +2046,8 @@
       <c r="C81" t="s">
         <v>159</v>
       </c>
-      <c r="D81">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>229</v>
       </c>
@@ -2386,12 +2057,8 @@
       <c r="C82" t="s">
         <v>161</v>
       </c>
-      <c r="D82">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>231</v>
       </c>
@@ -2401,12 +2068,8 @@
       <c r="C83" t="s">
         <v>163</v>
       </c>
-      <c r="D83">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>232</v>
       </c>
@@ -2416,12 +2079,8 @@
       <c r="C84" t="s">
         <v>165</v>
       </c>
-      <c r="D84">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>233</v>
       </c>
@@ -2431,12 +2090,8 @@
       <c r="C85" t="s">
         <v>167</v>
       </c>
-      <c r="D85">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>236</v>
       </c>
@@ -2446,12 +2101,8 @@
       <c r="C86" t="s">
         <v>169</v>
       </c>
-      <c r="D86">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>246</v>
       </c>
@@ -2461,12 +2112,8 @@
       <c r="C87" t="s">
         <v>171</v>
       </c>
-      <c r="D87">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>250</v>
       </c>
@@ -2476,12 +2123,8 @@
       <c r="C88" t="s">
         <v>173</v>
       </c>
-      <c r="D88">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>251</v>
       </c>
@@ -2491,12 +2134,8 @@
       <c r="C89" t="s">
         <v>175</v>
       </c>
-      <c r="D89">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>254</v>
       </c>
@@ -2506,12 +2145,8 @@
       <c r="C90" t="s">
         <v>177</v>
       </c>
-      <c r="D90">
-        <f t="shared" si="3"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>258</v>
       </c>
@@ -2521,12 +2156,8 @@
       <c r="C91" t="s">
         <v>179</v>
       </c>
-      <c r="D91">
-        <f t="shared" ref="D91:D110" si="4">LEN(B91)-LEN(TRIM(B91))</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>271</v>
       </c>
@@ -2536,12 +2167,8 @@
       <c r="C92" t="s">
         <v>181</v>
       </c>
-      <c r="D92">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>272</v>
       </c>
@@ -2551,12 +2178,8 @@
       <c r="C93" t="s">
         <v>183</v>
       </c>
-      <c r="D93">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>275</v>
       </c>
@@ -2566,12 +2189,8 @@
       <c r="C94" t="s">
         <v>185</v>
       </c>
-      <c r="D94">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>279</v>
       </c>
@@ -2581,12 +2200,8 @@
       <c r="C95" t="s">
         <v>187</v>
       </c>
-      <c r="D95">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>282</v>
       </c>
@@ -2596,12 +2211,8 @@
       <c r="C96" t="s">
         <v>189</v>
       </c>
-      <c r="D96">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>286</v>
       </c>
@@ -2611,12 +2222,8 @@
       <c r="C97" t="s">
         <v>191</v>
       </c>
-      <c r="D97">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>289</v>
       </c>
@@ -2626,12 +2233,8 @@
       <c r="C98" t="s">
         <v>193</v>
       </c>
-      <c r="D98">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>291</v>
       </c>
@@ -2641,12 +2244,8 @@
       <c r="C99" t="s">
         <v>195</v>
       </c>
-      <c r="D99">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>294</v>
       </c>
@@ -2656,12 +2255,8 @@
       <c r="C100" t="s">
         <v>197</v>
       </c>
-      <c r="D100">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>297</v>
       </c>
@@ -2671,12 +2266,8 @@
       <c r="C101" t="s">
         <v>199</v>
       </c>
-      <c r="D101">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>299</v>
       </c>
@@ -2686,12 +2277,8 @@
       <c r="C102" t="s">
         <v>201</v>
       </c>
-      <c r="D102">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>300</v>
       </c>
@@ -2701,12 +2288,8 @@
       <c r="C103" t="s">
         <v>203</v>
       </c>
-      <c r="D103">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>304</v>
       </c>
@@ -2716,12 +2299,8 @@
       <c r="C104" t="s">
         <v>205</v>
       </c>
-      <c r="D104">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>305</v>
       </c>
@@ -2731,12 +2310,8 @@
       <c r="C105" t="s">
         <v>207</v>
       </c>
-      <c r="D105">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>306</v>
       </c>
@@ -2746,12 +2321,8 @@
       <c r="C106" t="s">
         <v>209</v>
       </c>
-      <c r="D106">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>308</v>
       </c>
@@ -2761,12 +2332,8 @@
       <c r="C107" t="s">
         <v>211</v>
       </c>
-      <c r="D107">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>311</v>
       </c>
@@ -2776,12 +2343,8 @@
       <c r="C108" t="s">
         <v>213</v>
       </c>
-      <c r="D108">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>316</v>
       </c>
@@ -2791,12 +2354,8 @@
       <c r="C109" t="s">
         <v>215</v>
       </c>
-      <c r="D109">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>317</v>
       </c>
@@ -2806,12 +2365,8 @@
       <c r="C110" t="s">
         <v>217</v>
       </c>
-      <c r="D110">
-        <f t="shared" si="4"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>324</v>
       </c>
@@ -2821,12 +2376,8 @@
       <c r="C111" t="s">
         <v>219</v>
       </c>
-      <c r="D111">
-        <f t="shared" ref="D111:D118" si="5">LEN(B111)-LEN(TRIM(B111))</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>325</v>
       </c>
@@ -2836,12 +2387,8 @@
       <c r="C112" t="s">
         <v>221</v>
       </c>
-      <c r="D112">
-        <f t="shared" si="5"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>326</v>
       </c>
@@ -2851,12 +2398,8 @@
       <c r="C113" t="s">
         <v>223</v>
       </c>
-      <c r="D113">
-        <f t="shared" si="5"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>328</v>
       </c>
@@ -2866,12 +2409,8 @@
       <c r="C114" t="s">
         <v>225</v>
       </c>
-      <c r="D114">
-        <f t="shared" si="5"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>329</v>
       </c>
@@ -2881,12 +2420,8 @@
       <c r="C115" t="s">
         <v>227</v>
       </c>
-      <c r="D115">
-        <f t="shared" si="5"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>330</v>
       </c>
@@ -2896,12 +2431,8 @@
       <c r="C116" t="s">
         <v>229</v>
       </c>
-      <c r="D116">
-        <f t="shared" si="5"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>331</v>
       </c>
@@ -2911,12 +2442,8 @@
       <c r="C117" t="s">
         <v>231</v>
       </c>
-      <c r="D117">
-        <f t="shared" si="5"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>332</v>
       </c>
@@ -2925,10 +2452,6 @@
       </c>
       <c r="C118" t="s">
         <v>233</v>
-      </c>
-      <c r="D118">
-        <f t="shared" si="5"/>
-        <v>32</v>
       </c>
     </row>
   </sheetData>
